--- a/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T15:03:25+00:00</t>
+    <t>2023-11-15T15:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T15:06:39+00:00</t>
+    <t>2023-11-17T10:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T10:12:47+00:00</t>
+    <t>2023-11-17T10:19:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
+++ b/ig/nr-cleaning/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5491" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4669" uniqueCount="674">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T10:19:41+00:00</t>
+    <t>2023-11-20T14:22:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1826,265 +1826,22 @@
     <t>RolePerson</t>
   </si>
   <si>
-    <t>The nature of the relationship. Rôle de la personne</t>
+    <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person-role</t>
   </si>
   <si>
-    <t>Patient.contact.relationship:RolePerson.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.system</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R260-HL7RoleClass/FHIR/TRE-R260-HL7RoleClass</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.version</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.code</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.display</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RolePerson.text</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
     <t>Patient.contact.relationship:RelatedPerson</t>
   </si>
   <si>
     <t>RelatedPerson</t>
   </si>
   <si>
-    <t>The nature of the relationship. Relation de la personne</t>
+    <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-related-person</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.id</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.extension</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.system</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R216-HL7RoleCode/FHIR/TRE-R216-HL7RoleCode</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.version</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.code</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.display</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Patient.contact.relationship:RelatedPerson.text</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -2678,11 +2435,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO146"/>
+  <dimension ref="A1:AO124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.48046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="45.59375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.86328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.47265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.2265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -14845,9 +14602,11 @@
         <v>576</v>
       </c>
       <c r="B104" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>79</v>
       </c>
@@ -14868,16 +14627,20 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>104</v>
+        <v>578</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
       </c>
@@ -14901,13 +14664,11 @@
         <v>79</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>79</v>
+        <v>579</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>79</v>
@@ -14925,31 +14686,31 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>106</v>
+        <v>563</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AL104" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AL104" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>79</v>
+        <v>571</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>79</v>
@@ -14957,21 +14718,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>79</v>
@@ -14983,18 +14744,20 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>111</v>
+        <v>581</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>112</v>
+        <v>582</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -15030,34 +14793,34 @@
         <v>79</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>117</v>
+        <v>580</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>101</v>
+        <v>585</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>79</v>
@@ -15066,7 +14829,7 @@
         <v>79</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>79</v>
+        <v>586</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>79</v>
@@ -15074,10 +14837,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15097,22 +14860,22 @@
         <v>79</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>147</v>
+        <v>474</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>582</v>
+        <v>475</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>583</v>
+        <v>476</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>585</v>
+        <v>478</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -15161,7 +14924,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -15173,10 +14936,10 @@
         <v>99</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>100</v>
+        <v>479</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>587</v>
+        <v>480</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
@@ -15185,7 +14948,7 @@
         <v>79</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>588</v>
+        <v>481</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
@@ -15196,7 +14959,7 @@
         <v>589</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15219,16 +14982,20 @@
         <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>590</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>104</v>
+        <v>591</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
       </c>
@@ -15276,7 +15043,7 @@
         <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>106</v>
+        <v>589</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -15285,22 +15052,22 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AL107" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AL107" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AM107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>79</v>
+        <v>595</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>79</v>
@@ -15308,21 +15075,21 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>79</v>
@@ -15334,18 +15101,20 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>111</v>
+        <v>483</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>112</v>
+        <v>597</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
       </c>
@@ -15369,55 +15138,55 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>79</v>
+        <v>488</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>117</v>
+        <v>596</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>101</v>
+        <v>489</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>79</v>
+        <v>599</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>79</v>
@@ -15425,10 +15194,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15436,7 +15205,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>87</v>
@@ -15448,22 +15217,22 @@
         <v>79</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>131</v>
+        <v>321</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>79</v>
@@ -15473,7 +15242,7 @@
         <v>79</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>599</v>
+        <v>79</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>79</v>
@@ -15521,22 +15290,22 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>99</v>
+        <v>605</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>79</v>
@@ -15544,10 +15313,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15567,19 +15336,19 @@
         <v>79</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>103</v>
+        <v>311</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>607</v>
+        <v>314</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15641,19 +15410,19 @@
         <v>99</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>100</v>
+        <v>316</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>79</v>
@@ -15661,10 +15430,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15675,7 +15444,7 @@
         <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>79</v>
@@ -15684,22 +15453,22 @@
         <v>79</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>171</v>
+        <v>539</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>440</v>
+        <v>616</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>79</v>
@@ -15748,13 +15517,13 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>99</v>
@@ -15763,16 +15532,16 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>79</v>
+        <v>619</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>618</v>
+        <v>79</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>79</v>
@@ -15780,7 +15549,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>620</v>
@@ -15803,23 +15572,19 @@
         <v>79</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>621</v>
+        <v>104</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>79</v>
       </c>
@@ -15867,7 +15632,7 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>624</v>
+        <v>106</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -15876,13 +15641,13 @@
         <v>87</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>625</v>
+        <v>107</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>79</v>
@@ -15891,7 +15656,7 @@
         <v>79</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>626</v>
+        <v>79</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>79</v>
@@ -15899,21 +15664,21 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -15922,23 +15687,21 @@
         <v>79</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>371</v>
+        <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>629</v>
+        <v>111</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>630</v>
+        <v>112</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>632</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>79</v>
       </c>
@@ -15974,34 +15737,34 @@
         <v>79</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>633</v>
+        <v>117</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>634</v>
+        <v>101</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>79</v>
@@ -16010,7 +15773,7 @@
         <v>79</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>635</v>
+        <v>79</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>79</v>
@@ -16018,45 +15781,45 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>79</v>
+        <v>559</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>638</v>
+        <v>560</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>639</v>
+        <v>561</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>640</v>
+        <v>113</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>641</v>
+        <v>245</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
@@ -16105,22 +15868,22 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>642</v>
+        <v>562</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>643</v>
+        <v>101</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>79</v>
@@ -16129,7 +15892,7 @@
         <v>79</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>644</v>
+        <v>79</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>79</v>
@@ -16137,20 +15900,18 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>87</v>
@@ -16168,16 +15929,16 @@
         <v>280</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>647</v>
+        <v>624</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>565</v>
+        <v>625</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>514</v>
+        <v>626</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>566</v>
+        <v>627</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -16202,11 +15963,13 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>648</v>
+        <v>177</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>79</v>
@@ -16224,13 +15987,13 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>563</v>
+        <v>623</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>99</v>
@@ -16239,16 +16002,16 @@
         <v>100</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>107</v>
+        <v>629</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>571</v>
+        <v>630</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>79</v>
@@ -16256,10 +16019,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>577</v>
+        <v>631</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16282,16 +16045,20 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>103</v>
+        <v>371</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>104</v>
+        <v>632</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>633</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>635</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
       </c>
@@ -16339,7 +16106,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>106</v>
+        <v>631</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -16348,22 +16115,22 @@
         <v>87</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>107</v>
+        <v>636</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>79</v>
+        <v>637</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>79</v>
+        <v>638</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -16371,14 +16138,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>579</v>
+        <v>639</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>109</v>
+        <v>640</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16397,16 +16164,16 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>110</v>
+        <v>641</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>111</v>
+        <v>642</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>112</v>
+        <v>643</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>113</v>
+        <v>644</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16444,19 +16211,19 @@
         <v>79</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>117</v>
+        <v>639</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -16468,19 +16235,19 @@
         <v>99</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>118</v>
+        <v>326</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>101</v>
+        <v>645</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>79</v>
+        <v>646</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>79</v>
@@ -16488,10 +16255,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16502,7 +16269,7 @@
         <v>77</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>79</v>
@@ -16514,19 +16281,19 @@
         <v>88</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>147</v>
+        <v>648</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>582</v>
+        <v>649</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>583</v>
+        <v>650</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>584</v>
+        <v>651</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>585</v>
+        <v>652</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
@@ -16575,31 +16342,31 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>586</v>
+        <v>647</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>79</v>
+        <v>653</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>588</v>
+        <v>79</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>79</v>
@@ -16607,10 +16374,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>590</v>
+        <v>654</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16621,28 +16388,32 @@
         <v>77</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>103</v>
+        <v>539</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>104</v>
+        <v>655</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>658</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
       </c>
@@ -16690,25 +16461,25 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>106</v>
+        <v>654</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AL119" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>79</v>
@@ -16722,21 +16493,21 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>592</v>
+        <v>660</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
@@ -16748,17 +16519,15 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>79</v>
@@ -16795,34 +16564,34 @@
         <v>79</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>79</v>
@@ -16839,21 +16608,21 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>594</v>
+        <v>661</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -16862,23 +16631,21 @@
         <v>79</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>595</v>
+        <v>111</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>596</v>
+        <v>112</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
       </c>
@@ -16887,7 +16654,7 @@
         <v>79</v>
       </c>
       <c r="S121" t="s" s="2">
-        <v>655</v>
+        <v>79</v>
       </c>
       <c r="T121" t="s" s="2">
         <v>79</v>
@@ -16914,34 +16681,34 @@
         <v>79</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>600</v>
+        <v>117</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>601</v>
+        <v>101</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>79</v>
@@ -16950,7 +16717,7 @@
         <v>79</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>602</v>
+        <v>79</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -16958,44 +16725,46 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>79</v>
+        <v>559</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J122" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>605</v>
+        <v>560</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>606</v>
+        <v>561</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
@@ -17043,22 +16812,22 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>608</v>
+        <v>562</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>609</v>
+        <v>101</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>79</v>
@@ -17067,7 +16836,7 @@
         <v>79</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>610</v>
+        <v>79</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17075,10 +16844,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>612</v>
+        <v>663</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17086,7 +16855,7 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G123" t="s" s="2">
         <v>87</v>
@@ -17101,20 +16870,18 @@
         <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>171</v>
+        <v>664</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>613</v>
+        <v>665</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>614</v>
+        <v>666</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>615</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>79</v>
       </c>
@@ -17162,10 +16929,10 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>616</v>
+        <v>663</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH123" t="s" s="2">
         <v>87</v>
@@ -17174,19 +16941,19 @@
         <v>99</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>100</v>
+        <v>326</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>617</v>
+        <v>254</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>618</v>
+        <v>668</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17194,10 +16961,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>620</v>
+        <v>669</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17205,7 +16972,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>87</v>
@@ -17220,20 +16987,18 @@
         <v>88</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>621</v>
+        <v>670</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>622</v>
+        <v>671</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="O124" t="s" s="2">
-        <v>623</v>
-      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>79</v>
       </c>
@@ -17257,13 +17022,13 @@
         <v>79</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>79</v>
+        <v>671</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>79</v>
+        <v>672</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>79</v>
@@ -17281,10 +17046,10 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>624</v>
+        <v>669</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>87</v>
@@ -17296,2616 +17061,18 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>625</v>
+        <v>673</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>626</v>
+        <v>79</v>
       </c>
       <c r="AO124" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="P133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="P137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="P138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="P140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="B145" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G145" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J145" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K145" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="L145" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="O145" s="2"/>
-      <c r="P145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q145" s="2"/>
-      <c r="R145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF145" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ145" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN145" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AO145" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="B146" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E146" s="2"/>
-      <c r="F146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J146" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K146" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L146" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O146" s="2"/>
-      <c r="P146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q146" s="2"/>
-      <c r="R146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="AL146" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AM146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN146" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO146" t="s" s="2">
         <v>79</v>
       </c>
     </row>
